--- a/data/trans_dic/P32B-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P32B-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha sentido mal o culpable por su forma de beber</t>
+          <t>Población que se ha sentido mal o culpable por su forma de beber (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,46</t>
+          <t>0,21; 2,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,66</t>
+          <t>1,01; 3,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,16</t>
+          <t>0,45; 2,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,88</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,56</t>
+          <t>0,15; 1,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,48</t>
+          <t>0,76; 2,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,37</t>
+          <t>0,48; 2,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,49</t>
+          <t>0,23; 1,53</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,89</t>
+          <t>0,33; 1,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,96</t>
+          <t>1,08; 3,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,98</t>
+          <t>1,82; 5,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 5,19</t>
+          <t>1,34; 5,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,63</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,85</t>
+          <t>1,1; 6,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,66</t>
+          <t>0,35; 1,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,69</t>
+          <t>0,92; 2,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,4</t>
+          <t>1,36; 3,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,45</t>
+          <t>1,59; 4,54</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,25</t>
+          <t>0,23; 2,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,99</t>
+          <t>1,43; 4,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,77</t>
+          <t>0,25; 2,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,48</t>
+          <t>0,15; 2,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 3,91</t>
+          <t>0,04; 3,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,61</t>
+          <t>0,17; 1,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,63</t>
+          <t>1,1; 3,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,71</t>
+          <t>0,16; 1,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,32</t>
+          <t>0,24; 2,29</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,26</t>
+          <t>0,17; 2,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 6,76</t>
+          <t>2,83; 6,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,11</t>
+          <t>1,5; 4,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,44</t>
+          <t>1,62; 5,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,56</t>
+          <t>0,98; 4,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,63</t>
+          <t>0,31; 2,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,03</t>
+          <t>0,97; 4,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,25</t>
+          <t>0,35; 2,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,29</t>
+          <t>0,67; 2,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,54</t>
+          <t>2,11; 4,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,55</t>
+          <t>1,52; 3,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,82</t>
+          <t>1,34; 3,78</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,32</t>
+          <t>0,49; 1,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,65</t>
+          <t>2,17; 3,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,86</t>
+          <t>1,51; 2,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,92</t>
+          <t>1,35; 3,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,82</t>
+          <t>0,51; 2,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,38</t>
+          <t>0,3; 1,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,68</t>
+          <t>0,57; 1,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,4</t>
+          <t>0,58; 2,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,28</t>
+          <t>0,59; 1,32</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,73</t>
+          <t>1,61; 2,68</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,26</t>
+          <t>1,3; 2,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,35</t>
+          <t>1,13; 2,37</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha sentido mal o culpable por su forma de beber</t>
+          <t>Población que se ha sentido mal o culpable por su forma de beber (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>912; 10788</t>
+          <t>917; 11130</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4177; 15649</t>
+          <t>4339; 15713</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2701; 13595</t>
+          <t>1953; 12206</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>522; 6257</t>
+          <t>0; 5704</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1883</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2052</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4156</t>
+          <t>0; 3367</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4992</t>
+          <t>0; 4914</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>909; 9702</t>
+          <t>908; 10928</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4213; 14992</t>
+          <t>4574; 15113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3028; 14537</t>
+          <t>2935; 13695</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1121; 7342</t>
+          <t>1133; 7532</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1922; 10970</t>
+          <t>1902; 10803</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6510; 23578</t>
+          <t>6428; 22756</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10381; 28639</t>
+          <t>10432; 29135</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6575; 24729</t>
+          <t>6394; 25798</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 7321</t>
+          <t>0; 8822</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7139</t>
+          <t>0; 6985</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 8423</t>
+          <t>0; 6496</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2132; 11753</t>
+          <t>2201; 12231</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3072; 14248</t>
+          <t>2993; 14356</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8204; 24010</t>
+          <t>8233; 25765</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11906; 30471</t>
+          <t>12239; 31887</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10316; 30160</t>
+          <t>10740; 30767</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>771; 7437</t>
+          <t>770; 7194</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6019; 22933</t>
+          <t>6585; 22293</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1046; 11735</t>
+          <t>1045; 10222</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>490; 8080</t>
+          <t>484; 8400</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1838</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5654</t>
+          <t>0; 4991</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2012</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>212; 14721</t>
+          <t>159; 14640</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>773; 7429</t>
+          <t>769; 7200</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7090; 24193</t>
+          <t>7339; 23722</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1041; 11171</t>
+          <t>1042; 12201</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1550; 16282</t>
+          <t>1674; 16091</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>886; 11936</t>
+          <t>887; 10594</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16506; 37772</t>
+          <t>15848; 37359</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8086; 23634</t>
+          <t>8595; 24533</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7211; 24061</t>
+          <t>7172; 23268</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2969; 13921</t>
+          <t>2986; 14064</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1126; 9718</t>
+          <t>1133; 10615</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4149; 16433</t>
+          <t>3966; 16503</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1215; 6497</t>
+          <t>1011; 7141</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5358; 19081</t>
+          <t>5615; 18946</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19989; 42206</t>
+          <t>19597; 43089</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15515; 34876</t>
+          <t>14911; 33940</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9786; 27952</t>
+          <t>9797; 27638</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8534; 24749</t>
+          <t>9219; 24710</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>43502; 74590</t>
+          <t>44262; 77238</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30624; 57266</t>
+          <t>30208; 58754</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20826; 46118</t>
+          <t>21348; 48429</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4061; 16261</t>
+          <t>4583; 18108</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3043; 14437</t>
+          <t>3117; 14522</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5964; 19275</t>
+          <t>6479; 19812</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6984; 24659</t>
+          <t>5925; 23663</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15956; 35383</t>
+          <t>16469; 36675</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>50990; 84477</t>
+          <t>49859; 82695</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39831; 71195</t>
+          <t>40930; 69369</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>29953; 61236</t>
+          <t>29293; 61773</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32B-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P32B-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,53</t>
+          <t>0,21; 2,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,67</t>
+          <t>1,07; 3,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,84</t>
+          <t>0,49; 2,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,16; 1,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,76</t>
+          <t>0,15; 1,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,5</t>
+          <t>0,74; 2,6</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,23</t>
+          <t>0,5; 2,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,53</t>
+          <t>0,19; 1,37</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,86</t>
+          <t>0,33; 1,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,82</t>
+          <t>1,06; 3,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,07</t>
+          <t>1,78; 4,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,41</t>
+          <t>1,19; 4,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 2,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,09</t>
+          <t>1,01; 5,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,67</t>
+          <t>0,35; 1,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,89</t>
+          <t>0,92; 2,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,56</t>
+          <t>1,32; 3,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,54</t>
+          <t>1,43; 4,15</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,18</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,85</t>
+          <t>1,37; 4,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,58</t>
+          <t>0,62; 4,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 3,89</t>
+          <t>0,71; 6,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,56</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,56</t>
+          <t>1,16; 3,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,87</t>
+          <t>0,16; 1,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,29</t>
+          <t>0,92; 4,07</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,0</t>
+          <t>0,17; 1,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,68</t>
+          <t>2,91; 6,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,27</t>
+          <t>1,5; 4,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,26</t>
+          <t>1,86; 5,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,61</t>
+          <t>0,98; 4,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,87</t>
+          <t>0,28; 2,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,04</t>
+          <t>1,16; 3,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,47</t>
+          <t>0,65; 4,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,27</t>
+          <t>0,73; 2,41</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,64</t>
+          <t>2,1; 4,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,45</t>
+          <t>1,55; 3,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,78</t>
+          <t>1,63; 4,31</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,31</t>
+          <t>0,45; 1,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,78</t>
+          <t>2,06; 3,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,93</t>
+          <t>1,56; 2,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,07</t>
+          <t>1,5; 3,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,02</t>
+          <t>0,55; 1,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,38</t>
+          <t>0,3; 1,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,73</t>
+          <t>0,54; 1,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,31</t>
+          <t>1,12; 3,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,32</t>
+          <t>0,6; 1,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,68</t>
+          <t>1,62; 2,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,2</t>
+          <t>1,3; 2,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,37</t>
+          <t>1,55; 2,87</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3286</t>
         </is>
       </c>
     </row>
@@ -1645,22 +1645,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>917; 11130</t>
+          <t>905; 10080</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4339; 15713</t>
+          <t>4592; 15711</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1953; 12206</t>
+          <t>2116; 12802</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5704</t>
+          <t>549; 5925</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1675,32 +1675,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3367</t>
+          <t>0; 4991</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4914</t>
+          <t>0; 4695</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>908; 10928</t>
+          <t>915; 12039</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4574; 15113</t>
+          <t>4485; 15702</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2935; 13695</t>
+          <t>3074; 13809</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1133; 7532</t>
+          <t>996; 7197</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12652</t>
+          <t>12338</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5368</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18020</t>
+          <t>18034</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1902; 10803</t>
+          <t>1909; 10677</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6428; 22756</t>
+          <t>6309; 23516</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10432; 29135</t>
+          <t>10232; 27942</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6394; 25798</t>
+          <t>5948; 22665</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 8822</t>
+          <t>0; 6801</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6985</t>
+          <t>0; 7060</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6496</t>
+          <t>0; 7112</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2201; 12231</t>
+          <t>2252; 12822</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2993; 14356</t>
+          <t>2979; 13502</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8233; 25765</t>
+          <t>8196; 25006</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12239; 31887</t>
+          <t>11851; 30439</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10740; 30767</t>
+          <t>10359; 30036</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6527</t>
+          <t>11458</t>
         </is>
       </c>
     </row>
@@ -2061,22 +2061,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>770; 7194</t>
+          <t>0; 7290</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6585; 22293</t>
+          <t>6300; 21875</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1045; 10222</t>
+          <t>1042; 10204</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>484; 8400</t>
+          <t>2246; 15838</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4991</t>
+          <t>0; 5042</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2096,27 +2096,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>159; 14640</t>
+          <t>1426; 13275</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>769; 7200</t>
+          <t>0; 7612</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7339; 23722</t>
+          <t>7697; 22557</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1042; 12201</t>
+          <t>1049; 10170</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1674; 16091</t>
+          <t>5171; 22866</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13672</t>
+          <t>15432</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>20733</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>887; 10594</t>
+          <t>894; 10276</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15848; 37359</t>
+          <t>16251; 38634</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8595; 24533</t>
+          <t>8609; 23084</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7172; 23268</t>
+          <t>8650; 25431</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2986; 14064</t>
+          <t>2995; 14166</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1133; 10615</t>
+          <t>1028; 9875</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3966; 16503</t>
+          <t>4721; 16285</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1011; 7141</t>
+          <t>2011; 13463</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5615; 18946</t>
+          <t>6074; 20118</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19597; 43089</t>
+          <t>19547; 41629</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14911; 33940</t>
+          <t>15244; 33936</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9797; 27638</t>
+          <t>12587; 33256</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>36366</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13525</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>44472</t>
+          <t>53510</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9219; 24710</t>
+          <t>8433; 24419</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>44262; 77238</t>
+          <t>42163; 75862</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30208; 58754</t>
+          <t>31229; 57730</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21348; 48429</t>
+          <t>25195; 53349</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4583; 18108</t>
+          <t>4926; 17607</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3117; 14522</t>
+          <t>3102; 14773</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6479; 19812</t>
+          <t>6212; 20315</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5925; 23663</t>
+          <t>10156; 29995</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16469; 36675</t>
+          <t>16605; 36431</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49859; 82695</t>
+          <t>50203; 84351</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40930; 69369</t>
+          <t>40959; 69605</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>29293; 61773</t>
+          <t>40166; 74234</t>
         </is>
       </c>
     </row>
